--- a/astro-site/public/dl/ghost-kitchen-checklist-templates/03-ghost-kitchen-manager-checklist.xlsx
+++ b/astro-site/public/dl/ghost-kitchen-checklist-templates/03-ghost-kitchen-manager-checklist.xlsx
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B21" s="33" t="inlineStr">
         <is>
-          <t>Hood: filters — the team cleans the filters; the contractor cleans the ductwork ("Quarterly &amp; Annual" tab, NFPA 96)</t>
+          <t>Hood: the team degreases the filters every week ("Weekly Deep Clean" tab in 05); the technician checks the fan, belts and filters monthly; the contractor cleans the ductwork ("Quarterly &amp; Annual" tab, NFPA 96)</t>
         </is>
       </c>
       <c r="C21" s="27" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>Fryer oil condition and date of the last change (changed per the fryer manufacturer's instructions)</t>
+          <t>Fryer oil condition (last TPM reading) and date of the last change (changed when the TPM tester says, per the fryer manufacturer)</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
